--- a/sheets/조재수대금교본/검수/서른 즈음에.xlsx
+++ b/sheets/조재수대금교본/검수/서른 즈음에.xlsx
@@ -4782,11 +4782,7 @@
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
@@ -4884,11 +4880,7 @@
     </row>
     <row r="6" ht="90.37" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
@@ -5131,8 +5123,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -5153,11 +5144,7 @@
     </row>
     <row r="11" ht="90.37" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
@@ -5201,11 +5188,7 @@
         </is>
       </c>
       <c r="O11" s="24"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
@@ -5328,18 +5311,9 @@
     </row>
     <row r="14" ht="90.37" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21"/>
       <c r="G14" s="24"/>
@@ -5446,8 +5420,7 @@
       <c r="R15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-太
-‹</t>
+太</t>
         </is>
       </c>
       <c r="S15" s="22"/>
@@ -5629,8 +5602,7 @@
       <c r="M19" s="23"/>
       <c r="N19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O19" s="23"/>

--- a/sheets/조재수대금교본/검수/서른 즈음에.xlsx
+++ b/sheets/조재수대금교본/검수/서른 즈음에.xlsx
@@ -5311,7 +5311,11 @@
     </row>
     <row r="14" ht="90.37" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C14" s="24"/>
       <c r="D14" s="21"/>
       <c r="E14" s="24"/>

--- a/sheets/조재수대금교본/검수/서른 즈음에.xlsx
+++ b/sheets/조재수대금교본/검수/서른 즈음에.xlsx
@@ -4701,30 +4701,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="90.91" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="90.37" customHeight="true">
+    <row r="3" ht="70.93" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="90.37" customHeight="true">
+    <row r="4" ht="70.93" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="90.37" customHeight="true">
+    <row r="5" ht="70.93" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="90.37" customHeight="true">
+    <row r="6" ht="70.93" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="90.37" customHeight="true">
+    <row r="7" ht="70.93" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="90.37" customHeight="true">
+    <row r="8" ht="70.93" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="90.37" customHeight="true">
+    <row r="9" ht="70.93" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="90.37" customHeight="true">
+    <row r="10" ht="70.93" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="90.37" customHeight="true">
+    <row r="11" ht="70.93" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="90.37" customHeight="true">
+    <row r="12" ht="70.93" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="90.37" customHeight="true">
+    <row r="13" ht="70.93" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="90.37" customHeight="true">
+    <row r="14" ht="70.93" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" ht="90.37" customHeight="true">
+    <row r="15" ht="70.93" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="90.37" customHeight="true">
+    <row r="16" ht="70.93" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" ht="90.37" customHeight="true">
+    <row r="17" ht="70.93" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="24"/>
@@ -5527,7 +5527,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="24"/>
     </row>
-    <row r="18" ht="90.37" customHeight="true">
+    <row r="18" ht="70.93" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="S18" s="22"/>
     </row>
-    <row r="19" ht="90.37" customHeight="true">
+    <row r="19" ht="70.93" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       <c r="R19" s="21"/>
       <c r="S19" s="23"/>
     </row>
-    <row r="20" ht="90.37" customHeight="true">
+    <row r="20" ht="70.93" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="24"/>
@@ -5647,6 +5647,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>